--- a/first_aid_tema1_new/Таблица_изменений_Тема1_первая_помощь.xlsx
+++ b/first_aid_tema1_new/Таблица_изменений_Тема1_первая_помощь.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Изменения в презентациях" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Соответствие пунктов" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Изменения" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,36 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E30613"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F9FAFB"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -63,38 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D1D5DB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D1D5DB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D1D5DB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D1D5DB"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,394 +416,223 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Название презентации (без изменения)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Было (содержание / акцент)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Стало (под Прил. 2 № 2464 с 01.09.2026)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Пункт новой структуры</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Что изменено</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="75" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>1 Организационно-правовые аспекты оказания первой помощи.pptx</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Сводная тема 1 в старой компоновке (организация, НПА, понятие, наборы, последовательность, безопасность, извлечение, вызов)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Сводная тема 1, слайды разложены по пунктам 1.1–1.7 новой структуры с разделителями разделов</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Сводная тема 1 в старой компоновке</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Сводная тема 1 по пунктам 1.1–1.7 + оглавление, слайд приоритетности, терминология аптечек, резюме</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>1.1–1.7</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Перекомпоновка слайдов; добавлены разделители 1.1–1.7; обновлены подписи разделов; нумерация слайдов</t>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Перекомпоновка исходных слайдов; добавлены недостающие структурные и теоретические слайды</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="75" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>1.1_Понятие первая помощь.pptx</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Понятие «первая помощь»; перечень состояний; перечень мероприятий</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>То же имя файла. Внутри: определение (вводно) + состояния + мероприятия с акцентом на последовательность выполнения</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>п. 1.4 новой структуры
-(в старой нумерации файл остаётся 1.1)</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Имя файла не менялось. Добавлен акцент «последовательность выполнения мероприятий»; подпись к п. 1.4; нумерация слайдов</t>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Понятие ПП; состояния; мероприятия</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Содержание под п. 1.4 (состояния и мероприятия + последовательность)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>п. 1.4</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Подписи/акцент; имя файла сохранено</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="75" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>1.2_Современные наборы средств и устройств.pptx</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>«Современные наборы средств и устройств»; аптечка автомобильная; аптечка работникам</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Имя файла не менялось. Подпись приведена к новой терминологии: укладки, наборы, комплекты и аптечки</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Автомобильная аптечка; аптечка работникам</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>п. 1.2 + добавлен слайд терминологии «укладки, наборы, комплекты и аптечки»</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>п. 1.2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Имя файла не менялось. Обновлена служебная подпись (п. 1.2 / укладки–комплекты); визуальный контент прежний</t>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Добавлен недостающий теоретический слайд; визуалы аптечек сохранены</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="75" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>1.3_Общая последовательность действий на месте происшествия.pptx</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Общая последовательность действий на месте + способы извлечения и перемещения в одном файле</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Имя файла не менялось. Блок последовательности отмечен как п. 1.3 (порядок/приоритетность); блок извлечения — как п. 1.6</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>п. 1.3 + п. 1.6
-(в одном файле, без нового имени)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Имя файла не менялось. Разделены смысловые подписи: порядок/приоритетность и извлечение/перемещение; нумерация слайдов</t>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Последовательность + извлечение в одном файле</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>п. 1.3 (порядок/приоритетность) + п. 1.6 (извлечение) + слайд приоритетности</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>п. 1.3 и п. 1.6</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Добавлен слайд приоритетности; извлечение оставлено в том же файле (имя не менялось)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="75" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>1.4_Соблюдение правил личной безопасности.pptx</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Правила личной безопасности; обеспечение безопасных условий; профилактика инфекций</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Имя файла не менялось. Подпись приведена к п. 1.5 новой структуры (безопасные условия и профилактика инфекций)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>п. 1.5 новой структуры
-(в старой нумерации файл остаётся 1.4)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Имя файла не менялось. Обновлена подпись к п. 1.5; содержание слайдов сохранено; нумерация слайдов</t>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Безопасность и инфекции</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Подпись к п. 1.5 новой структуры</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>п. 1.5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Подписи; имя файла сохранено</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="75" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>1.5_Основные правила вызова скорой медицинской помощи.pptx</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Основные правила вызова СМП и других специальных служб</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Имя файла не менялось. Подпись приведена к п. 1.7 новой структуры</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>п. 1.7 новой структуры
-(в старой нумерации файл остаётся 1.5)</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Имя файла не менялось. Обновлена подпись к п. 1.7; содержание сохранено; нумерация слайдов</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Старый файл / блок</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Новый пункт Прил. 2 (с 01.09.2026)</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Сводная: организация и НПА</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>1.1 Нормативно-правовая база и организация оказания первой помощи</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>В отдельных файлах отдельной презентации 1.1 под НПА нет — только в сводной</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>1.2 Современные наборы…</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>1.2 Укладки, наборы, комплекты и аптечки</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Имя файла прежнее; терминология — в подписи</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>1.3 Общая последовательность… (алгоритм)</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>1.3 Порядок и приоритетность оказания первой помощи</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Имя файла прежнее</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>1.1 Понятие первая помощь (состояния/мероприятия)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>1.4 Перечень состояний и мероприятий + последовательность</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Имя файла осталось 1.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>1.4 Личная безопасность / инфекции</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>1.5 Безопасные условия и профилактика инфекций</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Имя файла осталось 1.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>1.3 … (извлечение и перемещение)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>1.6 Извлечение и перемещение пострадавших</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Отдельный файл не создавался; блок остался в 1.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>1.5 Основные правила вызова…</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>1.7 Правила вызова СМП и спецслужб</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Имя файла осталось 1.5</t>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Вызов СМП и спецслужб</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Подпись к п. 1.7 новой структуры</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>п. 1.7</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Подписи; имя файла сохранено</t>
         </is>
       </c>
     </row>
